--- a/evaluations/classification/classification_results_ensamble_test.xlsx
+++ b/evaluations/classification/classification_results_ensamble_test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>256</v>
       </c>
       <c r="H2" t="n">
         <v>128</v>
@@ -570,22 +570,22 @@
         <v>0.5</v>
       </c>
       <c r="N2" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>5.3</v>
+        <v>9.32</v>
       </c>
       <c r="Q2" t="n">
         <v>0.8903</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9256</v>
+        <v>0.9344</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8854</v>
+        <v>0.8832</v>
       </c>
     </row>
     <row r="3">
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>256</v>
       </c>
       <c r="H3" t="n">
         <v>128</v>
@@ -633,22 +633,22 @@
         <v>0.5</v>
       </c>
       <c r="N3" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.35</v>
+        <v>6.43</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8499</v>
+        <v>0.8676</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9029</v>
+        <v>0.9054</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.8593</v>
       </c>
     </row>
     <row r="4">
@@ -675,7 +675,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>16</v>
+        <v>256</v>
       </c>
       <c r="H4" t="n">
         <v>128</v>
@@ -696,22 +696,22 @@
         <v>0.5</v>
       </c>
       <c r="N4" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.99</v>
+        <v>3.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8701</v>
+        <v>0.8953</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9155</v>
+        <v>0.9458</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8575</v>
+        <v>0.8852</v>
       </c>
     </row>
     <row r="5">
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>16</v>
+        <v>256</v>
       </c>
       <c r="H5" t="n">
         <v>128</v>
@@ -759,85 +759,1597 @@
         <v>0.5</v>
       </c>
       <c r="N5" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.6</v>
+        <v>4.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8537</v>
+        <v>0.8789</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9105</v>
+        <v>0.9319</v>
       </c>
       <c r="S5" t="n">
-        <v>0.845</v>
+        <v>0.8685</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>BelugaID</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6909</v>
+      </c>
+      <c r="C6" t="n">
+        <v>747</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>256</v>
+      </c>
+      <c r="H6" t="n">
+        <v>128</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L6" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.0919</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.0727</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BelugaID</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6909</v>
+      </c>
+      <c r="C7" t="n">
+        <v>747</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>keynet_hardnet</t>
+        </is>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>256</v>
+      </c>
+      <c r="H7" t="n">
+        <v>128</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L7" t="n">
+        <v>10</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.0312</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.0861</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.0342</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BelugaID</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6909</v>
+      </c>
+      <c r="C8" t="n">
+        <v>747</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>256</v>
+      </c>
+      <c r="H8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20</v>
+      </c>
+      <c r="L8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.0484</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.0535</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>CowDataset</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B9" t="n">
         <v>1019</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C9" t="n">
         <v>12</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>256</v>
+      </c>
+      <c r="H9" t="n">
+        <v>128</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.9648</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.9837</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.969</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CowDataset</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1019</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>lightglue</t>
         </is>
       </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>16</v>
-      </c>
-      <c r="H6" t="n">
-        <v>128</v>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K6" t="n">
-        <v>20</v>
-      </c>
-      <c r="L6" t="n">
-        <v>10</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="O6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.8997000000000001</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.9566</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.9011</v>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>256</v>
+      </c>
+      <c r="H10" t="n">
+        <v>128</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.9675</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.9347</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Giraffes</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>906</v>
+      </c>
+      <c r="C11" t="n">
+        <v>170</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>256</v>
+      </c>
+      <c r="H11" t="n">
+        <v>128</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.2214</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2265</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1995</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Giraffes</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>906</v>
+      </c>
+      <c r="C12" t="n">
+        <v>170</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>lightglue</t>
+        </is>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>256</v>
+      </c>
+      <c r="H12" t="n">
+        <v>128</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.5115</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.5547</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.502</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Giraffes</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>906</v>
+      </c>
+      <c r="C13" t="n">
+        <v>170</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>256</v>
+      </c>
+      <c r="H13" t="n">
+        <v>128</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.4267</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Giraffes</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>906</v>
+      </c>
+      <c r="C14" t="n">
+        <v>170</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>keynet_hardnet</t>
+        </is>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>256</v>
+      </c>
+      <c r="H14" t="n">
+        <v>128</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1542</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HyenaID2022</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2497</v>
+      </c>
+      <c r="C15" t="n">
+        <v>247</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>256</v>
+      </c>
+      <c r="H15" t="n">
+        <v>128</v>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.6029</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.5762</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HyenaID2022</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2497</v>
+      </c>
+      <c r="C16" t="n">
+        <v>247</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>lightglue</t>
+        </is>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>256</v>
+      </c>
+      <c r="H16" t="n">
+        <v>128</v>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20</v>
+      </c>
+      <c r="L16" t="n">
+        <v>10</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.5273</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.6492</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4987</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HyenaID2022</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2497</v>
+      </c>
+      <c r="C17" t="n">
+        <v>247</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>256</v>
+      </c>
+      <c r="H17" t="n">
+        <v>128</v>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20</v>
+      </c>
+      <c r="L17" t="n">
+        <v>10</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.5125999999999999</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.6008</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.4871</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>IPanda50</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5499</v>
+      </c>
+      <c r="C18" t="n">
+        <v>48</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>keynet_hardnet</t>
+        </is>
+      </c>
+      <c r="E18" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>256</v>
+      </c>
+      <c r="H18" t="n">
+        <v>128</v>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20</v>
+      </c>
+      <c r="L18" t="n">
+        <v>10</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.7467</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.8673</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.7459</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>IPanda50</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5499</v>
+      </c>
+      <c r="C19" t="n">
+        <v>48</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E19" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>256</v>
+      </c>
+      <c r="H19" t="n">
+        <v>128</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20</v>
+      </c>
+      <c r="L19" t="n">
+        <v>10</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.7599</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.7574</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IPanda50</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5499</v>
+      </c>
+      <c r="C20" t="n">
+        <v>48</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E20" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>256</v>
+      </c>
+      <c r="H20" t="n">
+        <v>128</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O20" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.8146</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.9108000000000001</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.8128</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1498</v>
+      </c>
+      <c r="C21" t="n">
+        <v>227</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E21" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>256</v>
+      </c>
+      <c r="H21" t="n">
+        <v>128</v>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20</v>
+      </c>
+      <c r="L21" t="n">
+        <v>10</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O21" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.1561</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1352</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1498</v>
+      </c>
+      <c r="C22" t="n">
+        <v>227</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>keynet_hardnet</t>
+        </is>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>256</v>
+      </c>
+      <c r="H22" t="n">
+        <v>128</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20</v>
+      </c>
+      <c r="L22" t="n">
+        <v>10</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O22" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.1387</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.1167</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1498</v>
+      </c>
+      <c r="C23" t="n">
+        <v>227</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>lightglue</t>
+        </is>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>256</v>
+      </c>
+      <c r="H23" t="n">
+        <v>128</v>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K23" t="n">
+        <v>20</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.1069</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.2283</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.0823</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1498</v>
+      </c>
+      <c r="C24" t="n">
+        <v>227</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>256</v>
+      </c>
+      <c r="H24" t="n">
+        <v>128</v>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K24" t="n">
+        <v>20</v>
+      </c>
+      <c r="L24" t="n">
+        <v>10</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O24" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.1445</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1217</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1668</v>
+      </c>
+      <c r="C25" t="n">
+        <v>55</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>lightglue</t>
+        </is>
+      </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>256</v>
+      </c>
+      <c r="H25" t="n">
+        <v>128</v>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K25" t="n">
+        <v>20</v>
+      </c>
+      <c r="L25" t="n">
+        <v>10</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.6977</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.7806999999999999</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.673</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1668</v>
+      </c>
+      <c r="C26" t="n">
+        <v>55</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E26" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>256</v>
+      </c>
+      <c r="H26" t="n">
+        <v>128</v>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K26" t="n">
+        <v>20</v>
+      </c>
+      <c r="L26" t="n">
+        <v>10</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O26" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.7176</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.7874</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.6935</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>655</v>
+      </c>
+      <c r="C27" t="n">
+        <v>43</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E27" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>256</v>
+      </c>
+      <c r="H27" t="n">
+        <v>128</v>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K27" t="n">
+        <v>20</v>
+      </c>
+      <c r="L27" t="n">
+        <v>10</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O27" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.9913</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.9791</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>655</v>
+      </c>
+      <c r="C28" t="n">
+        <v>43</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E28" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>256</v>
+      </c>
+      <c r="H28" t="n">
+        <v>128</v>
+      </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K28" t="n">
+        <v>20</v>
+      </c>
+      <c r="L28" t="n">
+        <v>10</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O28" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.9913</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.9878</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>655</v>
+      </c>
+      <c r="C29" t="n">
+        <v>43</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>lightglue</t>
+        </is>
+      </c>
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>256</v>
+      </c>
+      <c r="H29" t="n">
+        <v>128</v>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K29" t="n">
+        <v>20</v>
+      </c>
+      <c r="L29" t="n">
+        <v>10</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O29" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.9043</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.9565</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.8963</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>655</v>
+      </c>
+      <c r="C30" t="n">
+        <v>43</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>keynet_hardnet</t>
+        </is>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>256</v>
+      </c>
+      <c r="H30" t="n">
+        <v>128</v>
+      </c>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K30" t="n">
+        <v>20</v>
+      </c>
+      <c r="L30" t="n">
+        <v>10</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O30" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.9739</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.9162</v>
       </c>
     </row>
   </sheetData>

--- a/evaluations/classification/classification_results_ensamble_test.xlsx
+++ b/evaluations/classification/classification_results_ensamble_test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,7 +791,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E6" t="b">
@@ -828,16 +828,16 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>12.24</v>
+        <v>11.29</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0484</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0919</v>
+        <v>0.073</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0727</v>
+        <v>0.0535</v>
       </c>
     </row>
     <row r="7">
@@ -854,7 +854,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>keynet_hardnet</t>
+          <t>lightglue</t>
         </is>
       </c>
       <c r="E7" t="b">
@@ -891,16 +891,16 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>9.4</v>
+        <v>5.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0312</v>
+        <v>0.023</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0861</v>
+        <v>0.0722</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0342</v>
+        <v>0.0283</v>
       </c>
     </row>
     <row r="8">
@@ -917,7 +917,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E8" t="b">
@@ -954,33 +954,33 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>11.29</v>
+        <v>12.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0484</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>0.073</v>
+        <v>0.0919</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0535</v>
+        <v>0.0727</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CowDataset</t>
+          <t>BelugaID</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1019</v>
+        <v>6909</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>747</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E9" t="b">
@@ -1017,16 +1017,16 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.72</v>
+        <v>9.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9648</v>
+        <v>0.0312</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9837</v>
+        <v>0.0861</v>
       </c>
       <c r="S9" t="n">
-        <v>0.969</v>
+        <v>0.0342</v>
       </c>
     </row>
     <row r="10">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>lightglue</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E10" t="b">
@@ -1080,33 +1080,33 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9648</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9675</v>
+        <v>0.9837</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9347</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Giraffes</t>
+          <t>CowDataset</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>906</v>
+        <v>1019</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>12</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E11" t="b">
@@ -1137,35 +1137,35 @@
         <v>0.5</v>
       </c>
       <c r="N11" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O11" t="b">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.93</v>
+        <v>97.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2214</v>
+        <v>0.7104</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2265</v>
+        <v>0.9044</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1995</v>
+        <v>0.7411</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Giraffes</t>
+          <t>CowDataset</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>906</v>
+        <v>1019</v>
       </c>
       <c r="C12" t="n">
-        <v>170</v>
+        <v>12</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1206,33 +1206,33 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.52</v>
+        <v>2.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5115</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5547</v>
+        <v>0.9675</v>
       </c>
       <c r="S12" t="n">
-        <v>0.502</v>
+        <v>0.9347</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Giraffes</t>
+          <t>CowDataset</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>906</v>
+        <v>1019</v>
       </c>
       <c r="C13" t="n">
-        <v>170</v>
+        <v>12</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E13" t="b">
@@ -1269,16 +1269,16 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>4.27</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4427</v>
+        <v>0.765</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4504</v>
+        <v>0.9044</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4267</v>
+        <v>0.7894</v>
       </c>
     </row>
     <row r="14">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>keynet_hardnet</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E14" t="b">
@@ -1332,33 +1332,33 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.29</v>
+        <v>2.93</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1756</v>
+        <v>0.2214</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3028</v>
+        <v>0.2265</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1542</v>
+        <v>0.1995</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HyenaID2022</t>
+          <t>Giraffes</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2497</v>
+        <v>906</v>
       </c>
       <c r="C15" t="n">
-        <v>247</v>
+        <v>170</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>lightglue</t>
         </is>
       </c>
       <c r="E15" t="b">
@@ -1395,33 +1395,33 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>5.46</v>
+        <v>1.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6029</v>
+        <v>0.5115</v>
       </c>
       <c r="R15" t="n">
-        <v>0.708</v>
+        <v>0.5547</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5762</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HyenaID2022</t>
+          <t>Giraffes</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2497</v>
+        <v>906</v>
       </c>
       <c r="C16" t="n">
-        <v>247</v>
+        <v>170</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>lightglue</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E16" t="b">
@@ -1458,33 +1458,33 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>4.27</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5273</v>
+        <v>0.4427</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6492</v>
+        <v>0.4504</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4987</v>
+        <v>0.4267</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HyenaID2022</t>
+          <t>Giraffes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2497</v>
+        <v>906</v>
       </c>
       <c r="C17" t="n">
-        <v>247</v>
+        <v>170</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E17" t="b">
@@ -1521,33 +1521,33 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.36</v>
+        <v>1.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.1756</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6008</v>
+        <v>0.3028</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4871</v>
+        <v>0.1542</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IPanda50</t>
+          <t>HyenaID2022</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5499</v>
+        <v>2497</v>
       </c>
       <c r="C18" t="n">
-        <v>48</v>
+        <v>247</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>keynet_hardnet</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E18" t="b">
@@ -1584,33 +1584,33 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>4.17</v>
+        <v>3.36</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.7467</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8673</v>
+        <v>0.6008</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7459</v>
+        <v>0.4871</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IPanda50</t>
+          <t>HyenaID2022</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5499</v>
+        <v>2497</v>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>247</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E19" t="b">
@@ -1647,33 +1647,33 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>8.369999999999999</v>
+        <v>5.46</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.7599</v>
+        <v>0.6029</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8571</v>
+        <v>0.708</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7574</v>
+        <v>0.5762</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IPanda50</t>
+          <t>HyenaID2022</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5499</v>
+        <v>2497</v>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>247</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>lightglue</t>
         </is>
       </c>
       <c r="E20" t="b">
@@ -1710,33 +1710,33 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>12.06</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8146</v>
+        <v>0.5273</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.6492</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8128</v>
+        <v>0.4987</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NyalaData</t>
+          <t>IPanda50</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1498</v>
+        <v>5499</v>
       </c>
       <c r="C21" t="n">
-        <v>227</v>
+        <v>48</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E21" t="b">
@@ -1773,33 +1773,33 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>4.36</v>
+        <v>4.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1561</v>
+        <v>0.7467</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3468</v>
+        <v>0.8673</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1352</v>
+        <v>0.7459</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NyalaData</t>
+          <t>IPanda50</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1498</v>
+        <v>5499</v>
       </c>
       <c r="C22" t="n">
-        <v>227</v>
+        <v>48</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>keynet_hardnet</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E22" t="b">
@@ -1836,33 +1836,33 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.63</v>
+        <v>12.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1387</v>
+        <v>0.8146</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2977</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1167</v>
+        <v>0.8128</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NyalaData</t>
+          <t>IPanda50</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1498</v>
+        <v>5499</v>
       </c>
       <c r="C23" t="n">
-        <v>227</v>
+        <v>48</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>lightglue</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E23" t="b">
@@ -1899,16 +1899,16 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.88</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1069</v>
+        <v>0.7599</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2283</v>
+        <v>0.8571</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0823</v>
+        <v>0.7574</v>
       </c>
     </row>
     <row r="24">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>keynet_hardnet</t>
         </is>
       </c>
       <c r="E24" t="b">
@@ -1962,29 +1962,29 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1445</v>
+        <v>0.1387</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3092</v>
+        <v>0.2977</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1217</v>
+        <v>0.1167</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1668</v>
+        <v>1498</v>
       </c>
       <c r="C25" t="n">
-        <v>55</v>
+        <v>227</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2025,29 +2025,29 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.6977</v>
+        <v>0.1069</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.2283</v>
       </c>
       <c r="S25" t="n">
-        <v>0.673</v>
+        <v>0.0823</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1668</v>
+        <v>1498</v>
       </c>
       <c r="C26" t="n">
-        <v>55</v>
+        <v>227</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2088,33 +2088,33 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.7176</v>
+        <v>0.1445</v>
       </c>
       <c r="R26" t="n">
-        <v>0.7874</v>
+        <v>0.3092</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6935</v>
+        <v>0.1217</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>StripeSpotter</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>655</v>
+        <v>1498</v>
       </c>
       <c r="C27" t="n">
-        <v>43</v>
+        <v>227</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E27" t="b">
@@ -2151,33 +2151,33 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.87</v>
+        <v>4.36</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9826</v>
+        <v>0.1561</v>
       </c>
       <c r="R27" t="n">
-        <v>0.9913</v>
+        <v>0.3468</v>
       </c>
       <c r="S27" t="n">
-        <v>0.9791</v>
+        <v>0.1352</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>StripeSpotter</t>
+          <t>SealID</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>655</v>
+        <v>1668</v>
       </c>
       <c r="C28" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>lightglue</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -2214,33 +2214,33 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9913</v>
+        <v>0.6977</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>0.9878</v>
+        <v>0.673</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>StripeSpotter</t>
+          <t>SealID</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>655</v>
+        <v>1668</v>
       </c>
       <c r="C29" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>lightglue</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E29" t="b">
@@ -2277,16 +2277,16 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9</v>
+        <v>2.19</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9043</v>
+        <v>0.7176</v>
       </c>
       <c r="R29" t="n">
-        <v>0.9565</v>
+        <v>0.7874</v>
       </c>
       <c r="S29" t="n">
-        <v>0.8963</v>
+        <v>0.6935</v>
       </c>
     </row>
     <row r="30">
@@ -2350,6 +2350,195 @@
       </c>
       <c r="S30" t="n">
         <v>0.9162</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>655</v>
+      </c>
+      <c r="C31" t="n">
+        <v>43</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E31" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>256</v>
+      </c>
+      <c r="H31" t="n">
+        <v>128</v>
+      </c>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K31" t="n">
+        <v>20</v>
+      </c>
+      <c r="L31" t="n">
+        <v>10</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O31" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.9913</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.9791</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>655</v>
+      </c>
+      <c r="C32" t="n">
+        <v>43</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E32" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>256</v>
+      </c>
+      <c r="H32" t="n">
+        <v>128</v>
+      </c>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K32" t="n">
+        <v>20</v>
+      </c>
+      <c r="L32" t="n">
+        <v>10</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O32" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.9913</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.9878</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>655</v>
+      </c>
+      <c r="C33" t="n">
+        <v>43</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>lightglue</t>
+        </is>
+      </c>
+      <c r="E33" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>256</v>
+      </c>
+      <c r="H33" t="n">
+        <v>128</v>
+      </c>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K33" t="n">
+        <v>20</v>
+      </c>
+      <c r="L33" t="n">
+        <v>10</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O33" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.9043</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.9565</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.8963</v>
       </c>
     </row>
   </sheetData>
